--- a/database/template-import-export/templates/template-peternakan.xlsx
+++ b/database/template-import-export/templates/template-peternakan.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
   <si>
     <t/>
   </si>
@@ -34,7 +34,7 @@
     <t>Populasi ternak, produksi daging/telur/susu-kulit, aliran ternak, dan pemotongan RPH.</t>
   </si>
   <si>
-    <t>Dibuat otomatis: 22/9/2026, 14.21.31</t>
+    <t>Dibuat otomatis: 29/9/2026, 15.29.41</t>
   </si>
   <si>
     <t>CARA PAKAI</t>
@@ -133,6 +133,9 @@
     <t>Kecamatan + Jenis + Tahun</t>
   </si>
   <si>
+    <t>Produksi (Butir)</t>
+  </si>
+  <si>
     <t>Sheet "Susu &amp; Kulit" — tabel ternak_susu_kulit</t>
   </si>
   <si>
@@ -220,10 +223,10 @@
     <t>Kambing</t>
   </si>
   <si>
+    <t>Itik</t>
+  </si>
+  <si>
     <t>Ayam Kampung</t>
-  </si>
-  <si>
-    <t>Ayam Ras Layer</t>
   </si>
   <si>
     <t>Kambing/Domba</t>
@@ -1089,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>30</v>
@@ -1105,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>0</v>
@@ -1182,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>30</v>
@@ -1193,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>26</v>
@@ -1209,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>0</v>
@@ -1223,7 +1226,7 @@
         <v>16</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1264,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1313,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>0</v>
@@ -1327,7 +1330,7 @@
         <v>16</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1368,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -1417,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>0</v>
@@ -1431,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -1442,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -1453,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -1464,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="C75" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -1475,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1497,16 +1500,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>29</v>
@@ -1530,16 +1533,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>29</v>
@@ -1547,13 +1550,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2">
         <v>2018</v>
@@ -1564,13 +1567,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>2018</v>
@@ -1581,7 +1584,7 @@
     </row>
     <row r="5" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1603,16 +1606,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>29</v>
@@ -1636,16 +1639,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>29</v>
@@ -1653,13 +1656,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2">
         <v>2018</v>
@@ -1670,13 +1673,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>2018</v>
@@ -1687,7 +1690,7 @@
     </row>
     <row r="5" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1707,16 +1710,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>29</v>
@@ -1740,16 +1743,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>29</v>
@@ -1757,13 +1760,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2">
         <v>2018</v>
@@ -1774,13 +1777,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3">
         <v>2018</v>
@@ -1791,7 +1794,7 @@
     </row>
     <row r="5" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1811,16 +1814,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>33</v>
@@ -1844,16 +1847,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>33</v>
@@ -1861,13 +1864,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2">
         <v>2018</v>
@@ -1878,13 +1881,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>2018</v>
@@ -1895,7 +1898,7 @@
     </row>
     <row r="5" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1910,21 +1913,21 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1940,49 +1943,49 @@
   <sheetData>
     <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2">
         <v>2018</v>
       </c>
       <c r="D2">
-        <v>1318876</v>
+        <v>82945</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3">
         <v>2018</v>
       </c>
       <c r="D3">
-        <v>1177600</v>
+        <v>1318876</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2001,19 +2004,19 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2029,27 +2032,27 @@
   <sheetData>
     <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2">
         <v>2018</v>
@@ -2058,15 +2061,15 @@
         <v>680</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3">
         <v>2018</v>
@@ -2075,12 +2078,12 @@
         <v>280</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
